--- a/dados/ES.xlsx
+++ b/dados/ES.xlsx
@@ -702,7 +702,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:AA763" headerRowCount="1" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:AA783" headerRowCount="1" dataDxfId="27">
   <autoFilter ref="A1:AA744"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID" dataDxfId="26"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA763"/>
+  <dimension ref="A1:AA783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7109375" customWidth="1" min="1" max="1"/>
@@ -85297,6 +85297,2206 @@
         </is>
       </c>
     </row>
+    <row r="764">
+      <c r="A764" s="20" t="inlineStr">
+        <is>
+          <t>ES2</t>
+        </is>
+      </c>
+      <c r="B764" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C764" s="20" t="inlineStr">
+        <is>
+          <t>ES-RIO_BANANAL</t>
+        </is>
+      </c>
+      <c r="D764" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E764" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F764" s="8" t="n">
+        <v>582.2628</v>
+      </c>
+      <c r="G764" s="8" t="n">
+        <v>12348.1</v>
+      </c>
+      <c r="H764" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I764" s="20" t="inlineStr">
+        <is>
+          <t>EMG8E81</t>
+        </is>
+      </c>
+      <c r="J764" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, SAULO ARAUJO DA SILVA</t>
+        </is>
+      </c>
+      <c r="K764" s="9" t="n">
+        <v>198.71</v>
+      </c>
+      <c r="L764" s="20" t="n"/>
+      <c r="M764" s="20" t="n"/>
+      <c r="N764" s="1" t="n"/>
+      <c r="O764" s="1" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="P764" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q764" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 08:54 BRT</t>
+        </is>
+      </c>
+      <c r="R764" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S764" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T764" s="20" t="inlineStr">
+        <is>
+          <t>julia.lima@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U764" s="20" t="n"/>
+      <c r="V764" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W764" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X764" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y764" s="19" t="n">
+        <v>0.3881752</v>
+      </c>
+      <c r="Z764" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA764" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="20" t="inlineStr">
+        <is>
+          <t>ES16</t>
+        </is>
+      </c>
+      <c r="B765" s="20" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C765" s="20" t="inlineStr">
+        <is>
+          <t>ES-MONTANHA-PINHEIROS</t>
+        </is>
+      </c>
+      <c r="D765" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E765" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F765" s="8" t="n">
+        <v>1394.6726</v>
+      </c>
+      <c r="G765" s="8" t="n">
+        <v>27531.28</v>
+      </c>
+      <c r="H765" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I765" s="20" t="inlineStr">
+        <is>
+          <t>UAE4A13</t>
+        </is>
+      </c>
+      <c r="J765" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, WAGNER GOMES PEIXOTO</t>
+        </is>
+      </c>
+      <c r="K765" s="9" t="n">
+        <v>357.82</v>
+      </c>
+      <c r="L765" s="20" t="n"/>
+      <c r="M765" s="20" t="n"/>
+      <c r="N765" s="1" t="n"/>
+      <c r="O765" s="1" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="P765" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q765" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:37 BRT</t>
+        </is>
+      </c>
+      <c r="R765" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S765" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T765" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U765" s="20" t="inlineStr">
+        <is>
+          <t>WAGNER GOMES PEIXOTO</t>
+        </is>
+      </c>
+      <c r="V765" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W765" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X765" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y765" s="19" t="n">
+        <v>0.9297817333333334</v>
+      </c>
+      <c r="Z765" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA765" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="20" t="inlineStr">
+        <is>
+          <t>ES25</t>
+        </is>
+      </c>
+      <c r="B766" s="20" t="inlineStr">
+        <is>
+          <t>RGB(238,130,238)</t>
+        </is>
+      </c>
+      <c r="C766" s="20" t="inlineStr">
+        <is>
+          <t>ES-MARATAIZES</t>
+        </is>
+      </c>
+      <c r="D766" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="E766" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="F766" s="8" t="n">
+        <v>777.1809</v>
+      </c>
+      <c r="G766" s="8" t="n">
+        <v>13270.657</v>
+      </c>
+      <c r="H766" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I766" s="20" t="inlineStr">
+        <is>
+          <t>SXN7J08</t>
+        </is>
+      </c>
+      <c r="J766" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALISSON NERES SANTANA</t>
+        </is>
+      </c>
+      <c r="K766" s="9" t="n">
+        <v>341.34</v>
+      </c>
+      <c r="L766" s="20" t="n"/>
+      <c r="M766" s="20" t="n"/>
+      <c r="N766" s="1" t="n"/>
+      <c r="O766" s="1" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="P766" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q766" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:00 BRT</t>
+        </is>
+      </c>
+      <c r="R766" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S766" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T766" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U766" s="20" t="inlineStr">
+        <is>
+          <t>ALISSON NERES SANTANA</t>
+        </is>
+      </c>
+      <c r="V766" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W766" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X766" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y766" s="19" t="n">
+        <v>0.1727068666666667</v>
+      </c>
+      <c r="Z766" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA766" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="20" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="B767" s="20" t="inlineStr">
+        <is>
+          <t>RGB(160,82,45)</t>
+        </is>
+      </c>
+      <c r="C767" s="20" t="inlineStr">
+        <is>
+          <t>ES-COLATINA-SAO_ROQUE</t>
+        </is>
+      </c>
+      <c r="D767" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E767" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F767" s="8" t="n">
+        <v>822.5163</v>
+      </c>
+      <c r="G767" s="8" t="n">
+        <v>17324.348</v>
+      </c>
+      <c r="H767" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I767" s="20" t="inlineStr">
+        <is>
+          <t>TPX3G84</t>
+        </is>
+      </c>
+      <c r="J767" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VITOR NASCIMENTO DE ARAUJO</t>
+        </is>
+      </c>
+      <c r="K767" s="9" t="n">
+        <v>145.87</v>
+      </c>
+      <c r="L767" s="20" t="n"/>
+      <c r="M767" s="20" t="n"/>
+      <c r="N767" s="1" t="n"/>
+      <c r="O767" s="1" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="P767" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q767" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:04 BRT</t>
+        </is>
+      </c>
+      <c r="R767" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S767" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T767" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U767" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VITOR NASCIMENTO DE ARAUJO </t>
+        </is>
+      </c>
+      <c r="V767" s="20" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="W767" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X767" s="20" t="inlineStr">
+        <is>
+          <t>Parada de Atendimento</t>
+        </is>
+      </c>
+      <c r="Y767" s="19" t="n">
+        <v>0.2741721</v>
+      </c>
+      <c r="Z767" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA767" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="20" t="inlineStr">
+        <is>
+          <t>ES26</t>
+        </is>
+      </c>
+      <c r="B768" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C768" s="20" t="inlineStr">
+        <is>
+          <t>ES-CACHOEIRO_ITAPEMIRIM</t>
+        </is>
+      </c>
+      <c r="D768" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E768" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F768" s="8" t="n">
+        <v>844.0596</v>
+      </c>
+      <c r="G768" s="8" t="n">
+        <v>18645.866</v>
+      </c>
+      <c r="H768" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I768" s="20" t="inlineStr">
+        <is>
+          <t>PWQ5C35</t>
+        </is>
+      </c>
+      <c r="J768" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VALMIRO DE OLIVEIRA NASCENTE</t>
+        </is>
+      </c>
+      <c r="K768" s="9" t="n">
+        <v>362.33</v>
+      </c>
+      <c r="L768" s="20" t="n"/>
+      <c r="M768" s="20" t="n"/>
+      <c r="N768" s="1" t="n"/>
+      <c r="O768" s="1" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="P768" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q768" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:04 BRT</t>
+        </is>
+      </c>
+      <c r="R768" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S768" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T768" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U768" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALMIRO DE OLIVEIRA NASCENTE </t>
+        </is>
+      </c>
+      <c r="V768" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W768" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X768" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y768" s="19" t="n">
+        <v>0.5627064000000001</v>
+      </c>
+      <c r="Z768" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA768" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="20" t="inlineStr">
+        <is>
+          <t>ES18</t>
+        </is>
+      </c>
+      <c r="B769" s="20" t="inlineStr">
+        <is>
+          <t>RGB(255,0,0)</t>
+        </is>
+      </c>
+      <c r="C769" s="20" t="inlineStr">
+        <is>
+          <t>ES-VITORIA</t>
+        </is>
+      </c>
+      <c r="D769" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="E769" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F769" s="8" t="n">
+        <v>1571.165</v>
+      </c>
+      <c r="G769" s="8" t="n">
+        <v>28376.65</v>
+      </c>
+      <c r="H769" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I769" s="20" t="inlineStr">
+        <is>
+          <t>RYY6A10</t>
+        </is>
+      </c>
+      <c r="J769" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GIDEVALDO DE AVELAR CONCEICAO</t>
+        </is>
+      </c>
+      <c r="K769" s="9" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="L769" s="20" t="n"/>
+      <c r="M769" s="20" t="n"/>
+      <c r="N769" s="1" t="n"/>
+      <c r="O769" s="1" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="P769" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q769" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 17:59 BRT</t>
+        </is>
+      </c>
+      <c r="R769" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S769" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T769" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U769" s="20" t="inlineStr">
+        <is>
+          <t>GIDEVALDO  DE AVELAR CONCEICAO</t>
+        </is>
+      </c>
+      <c r="V769" s="20" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="W769" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X769" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y769" s="19" t="n">
+        <v>0.5237216666666666</v>
+      </c>
+      <c r="Z769" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA769" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="20" t="inlineStr">
+        <is>
+          <t>ES20</t>
+        </is>
+      </c>
+      <c r="B770" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C770" s="20" t="inlineStr">
+        <is>
+          <t>ES-SERRA</t>
+        </is>
+      </c>
+      <c r="D770" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="E770" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F770" s="8" t="n">
+        <v>1460.0695</v>
+      </c>
+      <c r="G770" s="8" t="n">
+        <v>23692.393</v>
+      </c>
+      <c r="H770" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I770" s="20" t="inlineStr">
+        <is>
+          <t>RDN7A43</t>
+        </is>
+      </c>
+      <c r="J770" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ELIAS MARQUES SANTOS</t>
+        </is>
+      </c>
+      <c r="K770" s="9" t="n">
+        <v>181.03</v>
+      </c>
+      <c r="L770" s="20" t="n"/>
+      <c r="M770" s="20" t="n"/>
+      <c r="N770" s="1" t="n"/>
+      <c r="O770" s="1" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="P770" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q770" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 17:59 BRT</t>
+        </is>
+      </c>
+      <c r="R770" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S770" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T770" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U770" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIAS MARQUES SANTOS </t>
+        </is>
+      </c>
+      <c r="V770" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W770" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X770" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y770" s="19" t="n">
+        <v>0.3244598888888889</v>
+      </c>
+      <c r="Z770" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA770" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="20" t="inlineStr">
+        <is>
+          <t>ES29</t>
+        </is>
+      </c>
+      <c r="B771" s="20" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C771" s="20" t="inlineStr">
+        <is>
+          <t>ES-ALEGRE-GUACUI</t>
+        </is>
+      </c>
+      <c r="D771" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E771" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F771" s="8" t="n">
+        <v>1557.4564</v>
+      </c>
+      <c r="G771" s="8" t="n">
+        <v>28636.144</v>
+      </c>
+      <c r="H771" s="8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I771" s="20" t="inlineStr">
+        <is>
+          <t>ODD8C33</t>
+        </is>
+      </c>
+      <c r="J771" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, WERLISON SANTOS SILVA</t>
+        </is>
+      </c>
+      <c r="K771" s="9" t="n">
+        <v>374.26</v>
+      </c>
+      <c r="L771" s="20" t="n"/>
+      <c r="M771" s="20" t="n"/>
+      <c r="N771" s="1" t="n"/>
+      <c r="O771" s="1" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="P771" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q771" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:00 BRT</t>
+        </is>
+      </c>
+      <c r="R771" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S771" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T771" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U771" s="20" t="inlineStr">
+        <is>
+          <t>WERLISON SANTOS SILVA</t>
+        </is>
+      </c>
+      <c r="V771" s="20" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="W771" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X771" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y771" s="19" t="n">
+        <v>1.198043384615385</v>
+      </c>
+      <c r="Z771" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA771" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="20" t="inlineStr">
+        <is>
+          <t>ES1</t>
+        </is>
+      </c>
+      <c r="B772" s="20" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C772" s="20" t="inlineStr">
+        <is>
+          <t>ES-LINHARES</t>
+        </is>
+      </c>
+      <c r="D772" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="E772" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="F772" s="8" t="n">
+        <v>2429.9544</v>
+      </c>
+      <c r="G772" s="8" t="n">
+        <v>45496.546</v>
+      </c>
+      <c r="H772" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I772" s="20" t="inlineStr">
+        <is>
+          <t>SXN8A48</t>
+        </is>
+      </c>
+      <c r="J772" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ADEMILSON CORREIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="K772" s="9" t="n">
+        <v>116.02</v>
+      </c>
+      <c r="L772" s="20" t="n"/>
+      <c r="M772" s="20" t="n"/>
+      <c r="N772" s="1" t="n"/>
+      <c r="O772" s="1" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="P772" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q772" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:01 BRT</t>
+        </is>
+      </c>
+      <c r="R772" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S772" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T772" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U772" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADEMILSON CORREIA DA SILVA </t>
+        </is>
+      </c>
+      <c r="V772" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W772" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X772" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y772" s="19" t="n">
+        <v>0.5399898666666667</v>
+      </c>
+      <c r="Z772" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA772" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="20" t="inlineStr">
+        <is>
+          <t>ES28</t>
+        </is>
+      </c>
+      <c r="B773" s="20" t="inlineStr">
+        <is>
+          <t>RGB(255,215,0)</t>
+        </is>
+      </c>
+      <c r="C773" s="20" t="inlineStr">
+        <is>
+          <t>ES-MUNIZ_FREIRE</t>
+        </is>
+      </c>
+      <c r="D773" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="E773" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="F773" s="8" t="n">
+        <v>1207.5933</v>
+      </c>
+      <c r="G773" s="8" t="n">
+        <v>25200.79</v>
+      </c>
+      <c r="H773" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I773" s="20" t="inlineStr">
+        <is>
+          <t>NZR4F11</t>
+        </is>
+      </c>
+      <c r="J773" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALESSANDRO ANTONIO DA SILVA</t>
+        </is>
+      </c>
+      <c r="K773" s="9" t="n">
+        <v>545.41</v>
+      </c>
+      <c r="L773" s="20" t="n"/>
+      <c r="M773" s="20" t="n"/>
+      <c r="N773" s="1" t="n"/>
+      <c r="O773" s="1" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="P773" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q773" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 09:01 BRT</t>
+        </is>
+      </c>
+      <c r="R773" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S773" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T773" s="20" t="inlineStr">
+        <is>
+          <t>julia.lima@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U773" s="20" t="n"/>
+      <c r="V773" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W773" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X773" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y773" s="19" t="n">
+        <v>0.8050622</v>
+      </c>
+      <c r="Z773" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA773" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="20" t="inlineStr">
+        <is>
+          <t>ES30</t>
+        </is>
+      </c>
+      <c r="B774" s="20" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C774" s="20" t="inlineStr">
+        <is>
+          <t>ES-MUQUI_MIMOSO</t>
+        </is>
+      </c>
+      <c r="D774" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="E774" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="F774" s="8" t="n">
+        <v>1781.0063</v>
+      </c>
+      <c r="G774" s="8" t="n">
+        <v>31463.42</v>
+      </c>
+      <c r="H774" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I774" s="20" t="inlineStr">
+        <is>
+          <t>PPB2D54</t>
+        </is>
+      </c>
+      <c r="J774" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ELIELSON RIBEIRO LUXINGER</t>
+        </is>
+      </c>
+      <c r="K774" s="9" t="n">
+        <v>388.14</v>
+      </c>
+      <c r="L774" s="20" t="n"/>
+      <c r="M774" s="20" t="n"/>
+      <c r="N774" s="1" t="n"/>
+      <c r="O774" s="1" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="P774" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q774" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 08:54 BRT</t>
+        </is>
+      </c>
+      <c r="R774" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S774" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T774" s="20" t="inlineStr">
+        <is>
+          <t>julia.lima@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U774" s="20" t="n"/>
+      <c r="V774" s="20" t="inlineStr">
+        <is>
+          <t>3/4-IV</t>
+        </is>
+      </c>
+      <c r="W774" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X774" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y774" s="19" t="n">
+        <v>0.35620126</v>
+      </c>
+      <c r="Z774" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA774" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="20" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="B775" s="20" t="inlineStr">
+        <is>
+          <t>RGB(70,130,180)</t>
+        </is>
+      </c>
+      <c r="C775" s="20" t="inlineStr">
+        <is>
+          <t>ES-SAO_GABRIEL-VALERIO</t>
+        </is>
+      </c>
+      <c r="D775" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E775" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F775" s="8" t="n">
+        <v>1781.2695</v>
+      </c>
+      <c r="G775" s="8" t="n">
+        <v>34941.85</v>
+      </c>
+      <c r="H775" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I775" s="20" t="inlineStr">
+        <is>
+          <t>SXN8A08</t>
+        </is>
+      </c>
+      <c r="J775" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MURILO MARINHO VIEIRA</t>
+        </is>
+      </c>
+      <c r="K775" s="9" t="n">
+        <v>262.35</v>
+      </c>
+      <c r="L775" s="20" t="n"/>
+      <c r="M775" s="20" t="n"/>
+      <c r="N775" s="1" t="n"/>
+      <c r="O775" s="1" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="P775" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q775" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 17:57 BRT</t>
+        </is>
+      </c>
+      <c r="R775" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S775" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T775" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U775" s="20" t="inlineStr">
+        <is>
+          <t>MURILO MARINHO VIEIRA</t>
+        </is>
+      </c>
+      <c r="V775" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W775" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X775" s="20" t="inlineStr">
+        <is>
+          <t>Iniciado</t>
+        </is>
+      </c>
+      <c r="Y775" s="19" t="n">
+        <v>0.3958376666666667</v>
+      </c>
+      <c r="Z775" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA775" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="20" t="inlineStr">
+        <is>
+          <t>ES19</t>
+        </is>
+      </c>
+      <c r="B776" s="20" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C776" s="20" t="inlineStr">
+        <is>
+          <t>ES-VILA_VELHA</t>
+        </is>
+      </c>
+      <c r="D776" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E776" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F776" s="8" t="n">
+        <v>1721.7493</v>
+      </c>
+      <c r="G776" s="8" t="n">
+        <v>43765.133</v>
+      </c>
+      <c r="H776" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I776" s="20" t="inlineStr">
+        <is>
+          <t>QRE0B98</t>
+        </is>
+      </c>
+      <c r="J776" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GEORGE SANTANA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K776" s="9" t="n">
+        <v>162.28</v>
+      </c>
+      <c r="L776" s="20" t="n"/>
+      <c r="M776" s="20" t="n"/>
+      <c r="N776" s="1" t="n"/>
+      <c r="O776" s="1" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="P776" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q776" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 17:55 BRT</t>
+        </is>
+      </c>
+      <c r="R776" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S776" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T776" s="20" t="inlineStr">
+        <is>
+          <t>exceptiongeneratorprocess</t>
+        </is>
+      </c>
+      <c r="U776" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGE SANTANA DOS SANTOS </t>
+        </is>
+      </c>
+      <c r="V776" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W776" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X776" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y776" s="19" t="n">
+        <v>0.3826109555555555</v>
+      </c>
+      <c r="Z776" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA776" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="20" t="inlineStr">
+        <is>
+          <t>ES22</t>
+        </is>
+      </c>
+      <c r="B777" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C777" s="20" t="inlineStr">
+        <is>
+          <t>ES-GUARAPARI</t>
+        </is>
+      </c>
+      <c r="D777" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E777" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F777" s="8" t="n">
+        <v>2037.8672</v>
+      </c>
+      <c r="G777" s="8" t="n">
+        <v>39277.33</v>
+      </c>
+      <c r="H777" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I777" s="20" t="inlineStr">
+        <is>
+          <t>PLA2B93</t>
+        </is>
+      </c>
+      <c r="J777" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JORGE SANTOS DE ALMEIDA JUNIOR</t>
+        </is>
+      </c>
+      <c r="K777" s="9" t="n">
+        <v>172.64</v>
+      </c>
+      <c r="L777" s="20" t="n"/>
+      <c r="M777" s="20" t="n"/>
+      <c r="N777" s="1" t="n"/>
+      <c r="O777" s="1" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P777" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q777" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 08:54 BRT</t>
+        </is>
+      </c>
+      <c r="R777" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S777" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T777" s="20" t="inlineStr">
+        <is>
+          <t>julia.lima@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U777" s="20" t="n"/>
+      <c r="V777" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W777" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X777" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y777" s="19" t="n">
+        <v>0.4528593777777777</v>
+      </c>
+      <c r="Z777" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA777" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="20" t="inlineStr">
+        <is>
+          <t>ES10</t>
+        </is>
+      </c>
+      <c r="B778" s="20" t="inlineStr">
+        <is>
+          <t>RGB(32,178,170)</t>
+        </is>
+      </c>
+      <c r="C778" s="20" t="inlineStr">
+        <is>
+          <t>ES-PANCAS</t>
+        </is>
+      </c>
+      <c r="D778" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E778" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F778" s="8" t="n">
+        <v>1688.8729</v>
+      </c>
+      <c r="G778" s="8" t="n">
+        <v>29018.026</v>
+      </c>
+      <c r="H778" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I778" s="20" t="inlineStr">
+        <is>
+          <t>MTW4J36</t>
+        </is>
+      </c>
+      <c r="J778" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALEXANDRE DA ROCHA</t>
+        </is>
+      </c>
+      <c r="K778" s="9" t="n">
+        <v>747.08</v>
+      </c>
+      <c r="L778" s="20" t="n"/>
+      <c r="M778" s="20" t="n"/>
+      <c r="N778" s="1" t="n"/>
+      <c r="O778" s="1" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="P778" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q778" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:04 BRT</t>
+        </is>
+      </c>
+      <c r="R778" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S778" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T778" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U778" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEXANDRE DA ROCHA </t>
+        </is>
+      </c>
+      <c r="V778" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W778" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X778" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y778" s="19" t="n">
+        <v>1.125915266666667</v>
+      </c>
+      <c r="Z778" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA778" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="20" t="inlineStr">
+        <is>
+          <t>ES24</t>
+        </is>
+      </c>
+      <c r="B779" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C779" s="20" t="inlineStr">
+        <is>
+          <t>ES-VARGEM_ALTA -262- DOMINGO MARTINS</t>
+        </is>
+      </c>
+      <c r="D779" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E779" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F779" s="8" t="n">
+        <v>1268.6262</v>
+      </c>
+      <c r="G779" s="8" t="n">
+        <v>25571.399</v>
+      </c>
+      <c r="H779" s="8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I779" s="20" t="inlineStr">
+        <is>
+          <t>OYK3D99</t>
+        </is>
+      </c>
+      <c r="J779" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MANOEL ELISANDRO DA SILVA</t>
+        </is>
+      </c>
+      <c r="K779" s="9" t="n">
+        <v>773.73</v>
+      </c>
+      <c r="L779" s="20" t="n"/>
+      <c r="M779" s="20" t="n"/>
+      <c r="N779" s="1" t="n"/>
+      <c r="O779" s="1" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="P779" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q779" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 18:04 BRT</t>
+        </is>
+      </c>
+      <c r="R779" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S779" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T779" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U779" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANOEL ELISANDRO </t>
+        </is>
+      </c>
+      <c r="V779" s="20" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="W779" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X779" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y779" s="19" t="n">
+        <v>0.9758663076923076</v>
+      </c>
+      <c r="Z779" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA779" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="20" t="inlineStr">
+        <is>
+          <t>ES11</t>
+        </is>
+      </c>
+      <c r="B780" s="20" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C780" s="20" t="inlineStr">
+        <is>
+          <t>ES-BARRA_SAO_FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D780" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="E780" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F780" s="8" t="n">
+        <v>2272.6716</v>
+      </c>
+      <c r="G780" s="8" t="n">
+        <v>47315.241</v>
+      </c>
+      <c r="H780" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I780" s="20" t="inlineStr">
+        <is>
+          <t>SXK7D20</t>
+        </is>
+      </c>
+      <c r="J780" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RANDERSON JESUS DA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="K780" s="9" t="n">
+        <v>750.95</v>
+      </c>
+      <c r="L780" s="20" t="n"/>
+      <c r="M780" s="20" t="n"/>
+      <c r="N780" s="1" t="n"/>
+      <c r="O780" s="1" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="P780" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q780" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 17:58 BRT</t>
+        </is>
+      </c>
+      <c r="R780" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S780" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T780" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U780" s="20" t="inlineStr">
+        <is>
+          <t>RANDERSON JESUS DA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="V780" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W780" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X780" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y780" s="19" t="n">
+        <v>0.5050381333333334</v>
+      </c>
+      <c r="Z780" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA780" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="20" t="inlineStr">
+        <is>
+          <t>ES12</t>
+        </is>
+      </c>
+      <c r="B781" s="20" t="inlineStr">
+        <is>
+          <t>RGB(218,165,32)</t>
+        </is>
+      </c>
+      <c r="C781" s="20" t="inlineStr">
+        <is>
+          <t>ES-NOVA_VENECIA</t>
+        </is>
+      </c>
+      <c r="D781" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="E781" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="F781" s="8" t="n">
+        <v>1668.4173</v>
+      </c>
+      <c r="G781" s="8" t="n">
+        <v>34089.06</v>
+      </c>
+      <c r="H781" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I781" s="20" t="inlineStr">
+        <is>
+          <t>SXK7D10</t>
+        </is>
+      </c>
+      <c r="J781" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MARLON DE SOUZA</t>
+        </is>
+      </c>
+      <c r="K781" s="9" t="n">
+        <v>437.59</v>
+      </c>
+      <c r="L781" s="20" t="n"/>
+      <c r="M781" s="20" t="n"/>
+      <c r="N781" s="1" t="n"/>
+      <c r="O781" s="1" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="P781" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q781" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 08:54 BRT</t>
+        </is>
+      </c>
+      <c r="R781" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S781" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T781" s="20" t="inlineStr">
+        <is>
+          <t>julia.lima@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U781" s="20" t="n"/>
+      <c r="V781" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W781" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X781" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y781" s="19" t="n">
+        <v>0.3707594</v>
+      </c>
+      <c r="Z781" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA781" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="20" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="B782" s="20" t="inlineStr">
+        <is>
+          <t>RGB(205,92,92)</t>
+        </is>
+      </c>
+      <c r="C782" s="20" t="inlineStr">
+        <is>
+          <t>ES-STA_TEREZA-STA_MARIA</t>
+        </is>
+      </c>
+      <c r="D782" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="E782" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F782" s="8" t="n">
+        <v>2139.863</v>
+      </c>
+      <c r="G782" s="8" t="n">
+        <v>40563.744</v>
+      </c>
+      <c r="H782" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I782" s="20" t="inlineStr">
+        <is>
+          <t>SXN7C48</t>
+        </is>
+      </c>
+      <c r="J782" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DIRCEU DUTRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K782" s="9" t="n">
+        <v>482.88</v>
+      </c>
+      <c r="L782" s="20" t="n"/>
+      <c r="M782" s="20" t="n"/>
+      <c r="N782" s="1" t="n"/>
+      <c r="O782" s="1" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="P782" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q782" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 17:55 BRT</t>
+        </is>
+      </c>
+      <c r="R782" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S782" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:34 BRT</t>
+        </is>
+      </c>
+      <c r="T782" s="20" t="inlineStr">
+        <is>
+          <t>exceptiongeneratorprocess</t>
+        </is>
+      </c>
+      <c r="U782" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRCEU DUTRA DO SANTOS </t>
+        </is>
+      </c>
+      <c r="V782" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W782" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X782" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y782" s="19" t="n">
+        <v>0.4755251111111111</v>
+      </c>
+      <c r="Z782" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA782" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="20" t="inlineStr">
+        <is>
+          <t>ES17</t>
+        </is>
+      </c>
+      <c r="B783" s="20" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C783" s="20" t="inlineStr">
+        <is>
+          <t>ES-CARIACICA</t>
+        </is>
+      </c>
+      <c r="D783" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="E783" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F783" s="8" t="n">
+        <v>1394.5945</v>
+      </c>
+      <c r="G783" s="8" t="n">
+        <v>26757.039</v>
+      </c>
+      <c r="H783" s="8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I783" s="20" t="inlineStr">
+        <is>
+          <t>BBK7A74</t>
+        </is>
+      </c>
+      <c r="J783" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, CRISTIANO PENA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K783" s="9" t="n">
+        <v>119.31</v>
+      </c>
+      <c r="L783" s="20" t="n"/>
+      <c r="M783" s="20" t="n"/>
+      <c r="N783" s="1" t="n"/>
+      <c r="O783" s="1" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="P783" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q783" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 16:45 BRT</t>
+        </is>
+      </c>
+      <c r="R783" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S783" s="20" t="inlineStr">
+        <is>
+          <t>15/09/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="T783" s="20" t="inlineStr">
+        <is>
+          <t>routearchiveprocess</t>
+        </is>
+      </c>
+      <c r="U783" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRISTIANO PENA OLIVEIRA </t>
+        </is>
+      </c>
+      <c r="V783" s="20" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="W783" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 - ROTERIZAÇÃO - QUINTA</t>
+        </is>
+      </c>
+      <c r="X783" s="20" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="Y783" s="19" t="n">
+        <v>1.072765</v>
+      </c>
+      <c r="Z783" s="20" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="AA783" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/dados/ES.xlsx
+++ b/dados/ES.xlsx
@@ -702,7 +702,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:AA783" headerRowCount="1" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:AA796" headerRowCount="1" dataDxfId="27">
   <autoFilter ref="A1:AA744"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID" dataDxfId="26"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA783"/>
+  <dimension ref="A1:AA796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7109375" customWidth="1" min="1" max="1"/>
@@ -87497,6 +87497,1429 @@
         </is>
       </c>
     </row>
+    <row r="784">
+      <c r="A784" s="20" t="inlineStr">
+        <is>
+          <t>ES1</t>
+        </is>
+      </c>
+      <c r="B784" s="20" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C784" s="20" t="inlineStr">
+        <is>
+          <t>ES-LINHARES</t>
+        </is>
+      </c>
+      <c r="D784" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E784" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F784" s="8" t="n">
+        <v>2575.0475</v>
+      </c>
+      <c r="G784" s="8" t="n">
+        <v>41975.874</v>
+      </c>
+      <c r="H784" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I784" s="20" t="inlineStr">
+        <is>
+          <t>SXN8A48</t>
+        </is>
+      </c>
+      <c r="J784" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ADEMILSON CORREIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="K784" s="9" t="n">
+        <v>221.73</v>
+      </c>
+      <c r="L784" s="20" t="n"/>
+      <c r="M784" s="20" t="n"/>
+      <c r="N784" s="1" t="n"/>
+      <c r="O784" s="1" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="P784" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q784" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:56 BRT</t>
+        </is>
+      </c>
+      <c r="R784" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S784" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T784" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U784" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADEMILSON CORREIA DA SILVA </t>
+        </is>
+      </c>
+      <c r="V784" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W784" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X784" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y784" s="19" t="n">
+        <v>0.5722327777777778</v>
+      </c>
+      <c r="Z784" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA784" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="20" t="inlineStr">
+        <is>
+          <t>ES13</t>
+        </is>
+      </c>
+      <c r="B785" s="20" t="inlineStr">
+        <is>
+          <t>RGB(199,21,133)</t>
+        </is>
+      </c>
+      <c r="C785" s="20" t="inlineStr">
+        <is>
+          <t>ES-PEDRO_CANARIO-BARRA</t>
+        </is>
+      </c>
+      <c r="D785" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="E785" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="F785" s="8" t="n">
+        <v>1702.9843</v>
+      </c>
+      <c r="G785" s="8" t="n">
+        <v>36626.473</v>
+      </c>
+      <c r="H785" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I785" s="20" t="inlineStr">
+        <is>
+          <t>SXK7D10</t>
+        </is>
+      </c>
+      <c r="J785" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ADEILSON SILVA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K785" s="9" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="L785" s="20" t="n"/>
+      <c r="M785" s="20" t="n"/>
+      <c r="N785" s="1" t="n"/>
+      <c r="O785" s="1" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="P785" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q785" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 11:27 BRT</t>
+        </is>
+      </c>
+      <c r="R785" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S785" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T785" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U785" s="20" t="n"/>
+      <c r="V785" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W785" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X785" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y785" s="19" t="n">
+        <v>0.3784409555555556</v>
+      </c>
+      <c r="Z785" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA785" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="20" t="inlineStr">
+        <is>
+          <t>ES16</t>
+        </is>
+      </c>
+      <c r="B786" s="20" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C786" s="20" t="inlineStr">
+        <is>
+          <t>ES-CARIACICA</t>
+        </is>
+      </c>
+      <c r="D786" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E786" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F786" s="8" t="n">
+        <v>932.9933</v>
+      </c>
+      <c r="G786" s="8" t="n">
+        <v>16759.491</v>
+      </c>
+      <c r="H786" s="8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I786" s="20" t="inlineStr">
+        <is>
+          <t>BBK7A74</t>
+        </is>
+      </c>
+      <c r="J786" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, CRISTIANO PENA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K786" s="9" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="L786" s="20" t="n"/>
+      <c r="M786" s="20" t="n"/>
+      <c r="N786" s="1" t="n"/>
+      <c r="O786" s="1" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="P786" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q786" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:55 BRT</t>
+        </is>
+      </c>
+      <c r="R786" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S786" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T786" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U786" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRISTIANO PENA OLIVEIRA </t>
+        </is>
+      </c>
+      <c r="V786" s="20" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="W786" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X786" s="20" t="inlineStr">
+        <is>
+          <t>Parada de Atendimento</t>
+        </is>
+      </c>
+      <c r="Y786" s="19" t="n">
+        <v>0.7176871538461538</v>
+      </c>
+      <c r="Z786" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA786" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="20" t="inlineStr">
+        <is>
+          <t>ES17</t>
+        </is>
+      </c>
+      <c r="B787" s="20" t="inlineStr">
+        <is>
+          <t>RGB(255,0,0)</t>
+        </is>
+      </c>
+      <c r="C787" s="20" t="inlineStr">
+        <is>
+          <t>ES-VITORIA</t>
+        </is>
+      </c>
+      <c r="D787" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E787" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F787" s="8" t="n">
+        <v>386.1893</v>
+      </c>
+      <c r="G787" s="8" t="n">
+        <v>10087.33</v>
+      </c>
+      <c r="H787" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I787" s="20" t="inlineStr">
+        <is>
+          <t>RYY6A10</t>
+        </is>
+      </c>
+      <c r="J787" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GIDEVALDO DE AVELAR CONCEICAO</t>
+        </is>
+      </c>
+      <c r="K787" s="9" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="L787" s="20" t="n"/>
+      <c r="M787" s="20" t="n"/>
+      <c r="N787" s="1" t="n"/>
+      <c r="O787" s="1" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="P787" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q787" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:51 BRT</t>
+        </is>
+      </c>
+      <c r="R787" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S787" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T787" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U787" s="20" t="inlineStr">
+        <is>
+          <t>GIDEVALDO  DE AVELAR CONCEICAO</t>
+        </is>
+      </c>
+      <c r="V787" s="20" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="W787" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X787" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y787" s="19" t="n">
+        <v>0.1287297666666667</v>
+      </c>
+      <c r="Z787" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA787" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="20" t="inlineStr">
+        <is>
+          <t>ES18</t>
+        </is>
+      </c>
+      <c r="B788" s="20" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C788" s="20" t="inlineStr">
+        <is>
+          <t>ES-VILA_VELHA</t>
+        </is>
+      </c>
+      <c r="D788" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E788" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F788" s="8" t="n">
+        <v>2140.8962</v>
+      </c>
+      <c r="G788" s="8" t="n">
+        <v>40633.612</v>
+      </c>
+      <c r="H788" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I788" s="20" t="inlineStr">
+        <is>
+          <t>QRE0B98</t>
+        </is>
+      </c>
+      <c r="J788" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GEORGE SANTANA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K788" s="9" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="L788" s="20" t="n"/>
+      <c r="M788" s="20" t="n"/>
+      <c r="N788" s="1" t="n"/>
+      <c r="O788" s="1" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="P788" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q788" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:53 BRT</t>
+        </is>
+      </c>
+      <c r="R788" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S788" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T788" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U788" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGE SANTANA DOS SANTOS </t>
+        </is>
+      </c>
+      <c r="V788" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W788" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X788" s="20" t="inlineStr">
+        <is>
+          <t>Parada de Atendimento</t>
+        </is>
+      </c>
+      <c r="Y788" s="19" t="n">
+        <v>0.4757547111111111</v>
+      </c>
+      <c r="Z788" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA788" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="20" t="inlineStr">
+        <is>
+          <t>ES19</t>
+        </is>
+      </c>
+      <c r="B789" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C789" s="20" t="inlineStr">
+        <is>
+          <t>ES-SERRA</t>
+        </is>
+      </c>
+      <c r="D789" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E789" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="F789" s="8" t="n">
+        <v>2020.2704</v>
+      </c>
+      <c r="G789" s="8" t="n">
+        <v>36758.363</v>
+      </c>
+      <c r="H789" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I789" s="20" t="inlineStr">
+        <is>
+          <t>RDN7A43</t>
+        </is>
+      </c>
+      <c r="J789" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ELIAS MARQUES SANTOS</t>
+        </is>
+      </c>
+      <c r="K789" s="9" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="L789" s="20" t="n"/>
+      <c r="M789" s="20" t="n"/>
+      <c r="N789" s="1" t="n"/>
+      <c r="O789" s="1" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="P789" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q789" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:56 BRT</t>
+        </is>
+      </c>
+      <c r="R789" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S789" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T789" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U789" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIAS MARQUES SANTOS </t>
+        </is>
+      </c>
+      <c r="V789" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W789" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X789" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y789" s="19" t="n">
+        <v>0.4489489777777778</v>
+      </c>
+      <c r="Z789" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA789" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="20" t="inlineStr">
+        <is>
+          <t>ES20</t>
+        </is>
+      </c>
+      <c r="B790" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C790" s="20" t="inlineStr">
+        <is>
+          <t>ES-GUARAPARI</t>
+        </is>
+      </c>
+      <c r="D790" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E790" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F790" s="8" t="n">
+        <v>466.9116</v>
+      </c>
+      <c r="G790" s="8" t="n">
+        <v>9805.008</v>
+      </c>
+      <c r="H790" s="8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I790" s="20" t="inlineStr">
+        <is>
+          <t>QIL8C32</t>
+        </is>
+      </c>
+      <c r="J790" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, OTAVIO DE SOUZA</t>
+        </is>
+      </c>
+      <c r="K790" s="9" t="n">
+        <v>141.72</v>
+      </c>
+      <c r="L790" s="20" t="n"/>
+      <c r="M790" s="20" t="n"/>
+      <c r="N790" s="1" t="n"/>
+      <c r="O790" s="1" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="P790" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q790" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 11:27 BRT</t>
+        </is>
+      </c>
+      <c r="R790" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S790" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T790" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U790" s="20" t="n"/>
+      <c r="V790" s="20" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="W790" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X790" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y790" s="19" t="n">
+        <v>0.3591627692307692</v>
+      </c>
+      <c r="Z790" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA790" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="20" t="inlineStr">
+        <is>
+          <t>ES22</t>
+        </is>
+      </c>
+      <c r="B791" s="20" t="inlineStr">
+        <is>
+          <t>RGB(238,130,238)</t>
+        </is>
+      </c>
+      <c r="C791" s="20" t="inlineStr">
+        <is>
+          <t>ES-MARATAIZES</t>
+        </is>
+      </c>
+      <c r="D791" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E791" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F791" s="8" t="n">
+        <v>1265.0974</v>
+      </c>
+      <c r="G791" s="8" t="n">
+        <v>19027.69</v>
+      </c>
+      <c r="H791" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I791" s="20" t="inlineStr">
+        <is>
+          <t>SXN7J08</t>
+        </is>
+      </c>
+      <c r="J791" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, KEWEN CANDOTE HERINGER</t>
+        </is>
+      </c>
+      <c r="K791" s="9" t="n">
+        <v>192.39</v>
+      </c>
+      <c r="L791" s="20" t="n"/>
+      <c r="M791" s="20" t="n"/>
+      <c r="N791" s="1" t="n"/>
+      <c r="O791" s="1" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="P791" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q791" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:53 BRT</t>
+        </is>
+      </c>
+      <c r="R791" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S791" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T791" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U791" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEWEN CANDOTE HERINGER </t>
+        </is>
+      </c>
+      <c r="V791" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W791" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X791" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y791" s="19" t="n">
+        <v>0.2811327555555556</v>
+      </c>
+      <c r="Z791" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA791" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="20" t="inlineStr">
+        <is>
+          <t>ES24</t>
+        </is>
+      </c>
+      <c r="B792" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C792" s="20" t="inlineStr">
+        <is>
+          <t>ES-CACHOEIRO_ITAPEMIRIM</t>
+        </is>
+      </c>
+      <c r="D792" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E792" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F792" s="8" t="n">
+        <v>1441.0058</v>
+      </c>
+      <c r="G792" s="8" t="n">
+        <v>26879.22</v>
+      </c>
+      <c r="H792" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I792" s="20" t="inlineStr">
+        <is>
+          <t>PWQ5C35</t>
+        </is>
+      </c>
+      <c r="J792" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VALMIRO DE OLIVEIRA NASCENTE</t>
+        </is>
+      </c>
+      <c r="K792" s="9" t="n">
+        <v>284.71</v>
+      </c>
+      <c r="L792" s="20" t="n"/>
+      <c r="M792" s="20" t="n"/>
+      <c r="N792" s="1" t="n"/>
+      <c r="O792" s="1" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P792" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q792" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:56 BRT</t>
+        </is>
+      </c>
+      <c r="R792" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S792" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T792" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U792" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALMIRO DE OLIVEIRA NASCENTE </t>
+        </is>
+      </c>
+      <c r="V792" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W792" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X792" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y792" s="19" t="n">
+        <v>0.9606705333333333</v>
+      </c>
+      <c r="Z792" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA792" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="20" t="inlineStr">
+        <is>
+          <t>ES3</t>
+        </is>
+      </c>
+      <c r="B793" s="20" t="inlineStr">
+        <is>
+          <t>RGB(255,140,0)</t>
+        </is>
+      </c>
+      <c r="C793" s="20" t="inlineStr">
+        <is>
+          <t>ES-ARACRUZ</t>
+        </is>
+      </c>
+      <c r="D793" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E793" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="F793" s="8" t="n">
+        <v>1280.6967</v>
+      </c>
+      <c r="G793" s="8" t="n">
+        <v>30513.646</v>
+      </c>
+      <c r="H793" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I793" s="20" t="inlineStr">
+        <is>
+          <t>EMG8E81</t>
+        </is>
+      </c>
+      <c r="J793" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, SAULO ARAUJO DA SILVA</t>
+        </is>
+      </c>
+      <c r="K793" s="9" t="n">
+        <v>192.58</v>
+      </c>
+      <c r="L793" s="20" t="n"/>
+      <c r="M793" s="20" t="n"/>
+      <c r="N793" s="1" t="n"/>
+      <c r="O793" s="1" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="P793" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q793" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 11:27 BRT</t>
+        </is>
+      </c>
+      <c r="R793" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S793" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T793" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U793" s="20" t="n"/>
+      <c r="V793" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W793" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X793" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y793" s="19" t="n">
+        <v>0.8537977999999999</v>
+      </c>
+      <c r="Z793" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA793" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="20" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="B794" s="20" t="inlineStr">
+        <is>
+          <t>RGB(160,82,45)</t>
+        </is>
+      </c>
+      <c r="C794" s="20" t="inlineStr">
+        <is>
+          <t>ES-SAO_GABRIEL-VALERIO</t>
+        </is>
+      </c>
+      <c r="D794" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E794" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="F794" s="8" t="n">
+        <v>967.3598</v>
+      </c>
+      <c r="G794" s="8" t="n">
+        <v>23407.84</v>
+      </c>
+      <c r="H794" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I794" s="20" t="inlineStr">
+        <is>
+          <t>SXK7C60</t>
+        </is>
+      </c>
+      <c r="J794" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MURILO MARINHO VIEIRA</t>
+        </is>
+      </c>
+      <c r="K794" s="9" t="n">
+        <v>256.3</v>
+      </c>
+      <c r="L794" s="20" t="n"/>
+      <c r="M794" s="20" t="n"/>
+      <c r="N794" s="1" t="n"/>
+      <c r="O794" s="1" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="P794" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q794" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 11:27 BRT</t>
+        </is>
+      </c>
+      <c r="R794" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S794" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T794" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U794" s="20" t="n"/>
+      <c r="V794" s="20" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="W794" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X794" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y794" s="19" t="n">
+        <v>0.2149688444444444</v>
+      </c>
+      <c r="Z794" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA794" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="20" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="B795" s="20" t="inlineStr">
+        <is>
+          <t>RGB(70,130,180)</t>
+        </is>
+      </c>
+      <c r="C795" s="20" t="inlineStr">
+        <is>
+          <t>ES-SAO_MATEUS</t>
+        </is>
+      </c>
+      <c r="D795" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E795" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="F795" s="8" t="n">
+        <v>1296.6078</v>
+      </c>
+      <c r="G795" s="8" t="n">
+        <v>29440.212</v>
+      </c>
+      <c r="H795" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I795" s="20" t="inlineStr">
+        <is>
+          <t>MTW4J36</t>
+        </is>
+      </c>
+      <c r="J795" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, THIAGO KOSKI SEPULCHRO</t>
+        </is>
+      </c>
+      <c r="K795" s="9" t="n">
+        <v>422.87</v>
+      </c>
+      <c r="L795" s="20" t="n"/>
+      <c r="M795" s="20" t="n"/>
+      <c r="N795" s="1" t="n"/>
+      <c r="O795" s="1" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="P795" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q795" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 09:56 BRT</t>
+        </is>
+      </c>
+      <c r="R795" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S795" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="T795" s="20" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="U795" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIAGO KOSKI </t>
+        </is>
+      </c>
+      <c r="V795" s="20" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="W795" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X795" s="20" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="Y795" s="19" t="n">
+        <v>0.8644052</v>
+      </c>
+      <c r="Z795" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA795" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="20" t="inlineStr">
+        <is>
+          <t>ES-LINHARES</t>
+        </is>
+      </c>
+      <c r="B796" s="20" t="inlineStr">
+        <is>
+          <t>RGB(0,0,128)</t>
+        </is>
+      </c>
+      <c r="C796" s="20" t="inlineStr">
+        <is>
+          <t>ES-LINHARES 2</t>
+        </is>
+      </c>
+      <c r="D796" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E796" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F796" s="8" t="n">
+        <v>3215.2775</v>
+      </c>
+      <c r="G796" s="8" t="n">
+        <v>74249.66</v>
+      </c>
+      <c r="H796" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I796" s="20" t="inlineStr">
+        <is>
+          <t>ISR1467</t>
+        </is>
+      </c>
+      <c r="J796" s="20" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GEREMIAS QUIRINO DE JESUS</t>
+        </is>
+      </c>
+      <c r="K796" s="9" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="L796" s="20" t="n"/>
+      <c r="M796" s="20" t="n"/>
+      <c r="N796" s="1" t="n"/>
+      <c r="O796" s="1" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="P796" s="20" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="Q796" s="20" t="inlineStr">
+        <is>
+          <t>17/09/2026 11:27 BRT</t>
+        </is>
+      </c>
+      <c r="R796" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S796" s="20" t="inlineStr">
+        <is>
+          <t>16/09/2026 19:10 BRT</t>
+        </is>
+      </c>
+      <c r="T796" s="20" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="U796" s="20" t="n"/>
+      <c r="V796" s="20" t="inlineStr">
+        <is>
+          <t>VUC</t>
+        </is>
+      </c>
+      <c r="W796" s="20" t="inlineStr">
+        <is>
+          <t>18/09/2026 - ROTERIZACAO - SEXTA 18/09</t>
+        </is>
+      </c>
+      <c r="X796" s="20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Y796" s="19" t="n">
+        <v>1.461489772727273</v>
+      </c>
+      <c r="Z796" s="20" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="AA796" s="20" t="inlineStr">
+        <is>
+          <t>SET/S3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
